--- a/data/nzd0210/nzd0210.xlsx
+++ b/data/nzd0210/nzd0210.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W394"/>
+  <dimension ref="A1:W395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30016,6 +30016,81 @@
         <v>363.55</v>
       </c>
       <c r="W394" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:53:16+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>403.34</v>
+      </c>
+      <c r="C395" t="n">
+        <v>388.65</v>
+      </c>
+      <c r="D395" t="n">
+        <v>381.89</v>
+      </c>
+      <c r="E395" t="n">
+        <v>395.23</v>
+      </c>
+      <c r="F395" t="n">
+        <v>409.49</v>
+      </c>
+      <c r="G395" t="n">
+        <v>424.37</v>
+      </c>
+      <c r="H395" t="n">
+        <v>429.21</v>
+      </c>
+      <c r="I395" t="n">
+        <v>415.44</v>
+      </c>
+      <c r="J395" t="n">
+        <v>402.69</v>
+      </c>
+      <c r="K395" t="n">
+        <v>393.58</v>
+      </c>
+      <c r="L395" t="n">
+        <v>390.56</v>
+      </c>
+      <c r="M395" t="n">
+        <v>390.7</v>
+      </c>
+      <c r="N395" t="n">
+        <v>389.68</v>
+      </c>
+      <c r="O395" t="n">
+        <v>382.39</v>
+      </c>
+      <c r="P395" t="n">
+        <v>377.57</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>367.56</v>
+      </c>
+      <c r="R395" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="S395" t="n">
+        <v>366.21</v>
+      </c>
+      <c r="T395" t="n">
+        <v>372.71</v>
+      </c>
+      <c r="U395" t="n">
+        <v>363.11</v>
+      </c>
+      <c r="V395" t="n">
+        <v>363.28</v>
+      </c>
+      <c r="W395" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30032,7 +30107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B404"/>
+  <dimension ref="A1:B405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34075,6 +34150,16 @@
       </c>
       <c r="B404" t="n">
         <v>-0.35</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>-0.13</v>
       </c>
     </row>
   </sheetData>
@@ -34243,28 +34328,28 @@
         <v>0.0352</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2149587483813055</v>
+        <v>-0.2109966695444526</v>
       </c>
       <c r="J2" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K2" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1111683921615607</v>
+        <v>0.1074161730528898</v>
       </c>
       <c r="M2" t="n">
-        <v>3.679975313034944</v>
+        <v>3.690147123895121</v>
       </c>
       <c r="N2" t="n">
-        <v>19.21693268931046</v>
+        <v>19.3070708555563</v>
       </c>
       <c r="O2" t="n">
-        <v>4.383712204206666</v>
+        <v>4.39398120792025</v>
       </c>
       <c r="P2" t="n">
-        <v>401.6712454021783</v>
+        <v>401.6273311001974</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34321,28 +34406,28 @@
         <v>0.0504</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.003506344280547633</v>
+        <v>0.0005286817963480347</v>
       </c>
       <c r="J3" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K3" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L3" t="n">
-        <v>1.926472404312207e-05</v>
+        <v>4.38650678002972e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>4.630900934949568</v>
+        <v>4.63780123930361</v>
       </c>
       <c r="N3" t="n">
-        <v>33.19507142284504</v>
+        <v>33.25489428799948</v>
       </c>
       <c r="O3" t="n">
-        <v>5.761516416955265</v>
+        <v>5.766705670311211</v>
       </c>
       <c r="P3" t="n">
-        <v>381.1779350357653</v>
+        <v>381.1332122119806</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34399,28 +34484,28 @@
         <v>0.0418</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1440577934734603</v>
+        <v>0.1480745550367445</v>
       </c>
       <c r="J4" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K4" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03106878815449343</v>
+        <v>0.03281990565324522</v>
       </c>
       <c r="M4" t="n">
-        <v>4.525748806487287</v>
+        <v>4.533041968257304</v>
       </c>
       <c r="N4" t="n">
-        <v>33.66493674059548</v>
+        <v>33.72226570364149</v>
       </c>
       <c r="O4" t="n">
-        <v>5.802149320777214</v>
+        <v>5.807087540552621</v>
       </c>
       <c r="P4" t="n">
-        <v>370.4961306565286</v>
+        <v>370.4516102702519</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -34481,28 +34566,28 @@
         <v>0.0581</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2073399650806748</v>
+        <v>0.2116599174168961</v>
       </c>
       <c r="J5" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K5" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09312618829078279</v>
+        <v>0.09652037433144844</v>
       </c>
       <c r="M5" t="n">
-        <v>3.56186729793125</v>
+        <v>3.572813574129582</v>
       </c>
       <c r="N5" t="n">
-        <v>21.77593087457118</v>
+        <v>21.88580182559037</v>
       </c>
       <c r="O5" t="n">
-        <v>4.666468779984624</v>
+        <v>4.678226354676563</v>
       </c>
       <c r="P5" t="n">
-        <v>381.5718537272912</v>
+        <v>381.5239728800776</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34559,28 +34644,28 @@
         <v>0.0635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1443280884010734</v>
+        <v>0.1475064903206593</v>
       </c>
       <c r="J6" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K6" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07455196267425945</v>
+        <v>0.07755960029345854</v>
       </c>
       <c r="M6" t="n">
-        <v>3.042754563031964</v>
+        <v>3.050172352412159</v>
       </c>
       <c r="N6" t="n">
-        <v>13.4502491821868</v>
+        <v>13.50550613847808</v>
       </c>
       <c r="O6" t="n">
-        <v>3.667458136391852</v>
+        <v>3.674983828328783</v>
       </c>
       <c r="P6" t="n">
-        <v>399.6585825573529</v>
+        <v>399.6233542573972</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34637,28 +34722,28 @@
         <v>0.0512</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05526533980060136</v>
+        <v>0.05866650331816276</v>
       </c>
       <c r="J7" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K7" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008842468803938575</v>
+        <v>0.009954489223259255</v>
       </c>
       <c r="M7" t="n">
-        <v>3.401583670879599</v>
+        <v>3.406659182542626</v>
       </c>
       <c r="N7" t="n">
-        <v>17.80780912670536</v>
+        <v>17.86497603031886</v>
       </c>
       <c r="O7" t="n">
-        <v>4.219929990735078</v>
+        <v>4.226698005573483</v>
       </c>
       <c r="P7" t="n">
-        <v>416.5139538287391</v>
+        <v>416.4762565168109</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34715,28 +34800,28 @@
         <v>0.0457</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01734652878393778</v>
+        <v>-0.01194414065387266</v>
       </c>
       <c r="J8" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K8" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0007123095788316158</v>
+        <v>0.00033587652258249</v>
       </c>
       <c r="M8" t="n">
-        <v>3.696100018535287</v>
+        <v>3.710635550104565</v>
       </c>
       <c r="N8" t="n">
-        <v>21.95748370131248</v>
+        <v>22.16001897803164</v>
       </c>
       <c r="O8" t="n">
-        <v>4.685881315325057</v>
+        <v>4.707442934123752</v>
       </c>
       <c r="P8" t="n">
-        <v>419.5481169972911</v>
+        <v>419.4882388087111</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34793,28 +34878,28 @@
         <v>0.055</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1004643601887463</v>
+        <v>-0.09517608502737383</v>
       </c>
       <c r="J9" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K9" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02509710752785488</v>
+        <v>0.02244590394223756</v>
       </c>
       <c r="M9" t="n">
-        <v>3.595807417450156</v>
+        <v>3.613455418847179</v>
       </c>
       <c r="N9" t="n">
-        <v>20.39376388628435</v>
+        <v>20.58947272453306</v>
       </c>
       <c r="O9" t="n">
-        <v>4.515945514096063</v>
+        <v>4.537562421006796</v>
       </c>
       <c r="P9" t="n">
-        <v>408.2134756881915</v>
+        <v>408.1548622880152</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34871,28 +34956,28 @@
         <v>0.058</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1032450739708065</v>
+        <v>-0.0986241854014675</v>
       </c>
       <c r="J10" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K10" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02659867418542583</v>
+        <v>0.02424680365330678</v>
       </c>
       <c r="M10" t="n">
-        <v>3.640575217043379</v>
+        <v>3.651165463873729</v>
       </c>
       <c r="N10" t="n">
-        <v>20.29113204499714</v>
+        <v>20.42858082609955</v>
       </c>
       <c r="O10" t="n">
-        <v>4.504567908800703</v>
+        <v>4.519798759469226</v>
       </c>
       <c r="P10" t="n">
-        <v>396.7948233810313</v>
+        <v>396.7436070614148</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34949,28 +35034,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1837771980629882</v>
+        <v>-0.179922607285329</v>
       </c>
       <c r="J11" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K11" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07928674861081519</v>
+        <v>0.07620717519039522</v>
       </c>
       <c r="M11" t="n">
-        <v>3.631003174870469</v>
+        <v>3.639109075074707</v>
       </c>
       <c r="N11" t="n">
-        <v>20.40058825403925</v>
+        <v>20.48028730603269</v>
       </c>
       <c r="O11" t="n">
-        <v>4.516701036601741</v>
+        <v>4.52551514261445</v>
       </c>
       <c r="P11" t="n">
-        <v>391.2822333206641</v>
+        <v>391.2395103788973</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35027,28 +35112,28 @@
         <v>0.0613</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1514821329919254</v>
+        <v>-0.1480909874312359</v>
       </c>
       <c r="J12" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K12" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05387447855547689</v>
+        <v>0.05166267193349994</v>
       </c>
       <c r="M12" t="n">
-        <v>3.71879896710489</v>
+        <v>3.726661972316859</v>
       </c>
       <c r="N12" t="n">
-        <v>20.96158676644556</v>
+        <v>21.01014702799853</v>
       </c>
       <c r="O12" t="n">
-        <v>4.578382549159207</v>
+        <v>4.583682692769923</v>
       </c>
       <c r="P12" t="n">
-        <v>388.2639002266528</v>
+        <v>388.2263139502697</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35105,28 +35190,28 @@
         <v>0.0355</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2139544211957529</v>
+        <v>-0.2103143859894805</v>
       </c>
       <c r="J13" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K13" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05996139791750821</v>
+        <v>0.05820576415837908</v>
       </c>
       <c r="M13" t="n">
-        <v>4.822635985935999</v>
+        <v>4.830054426128003</v>
       </c>
       <c r="N13" t="n">
-        <v>37.32949571147255</v>
+        <v>37.35199869004775</v>
       </c>
       <c r="O13" t="n">
-        <v>6.109786879382336</v>
+        <v>6.111628153777661</v>
       </c>
       <c r="P13" t="n">
-        <v>389.615106592136</v>
+        <v>389.5747617096005</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35183,28 +35268,28 @@
         <v>0.0322</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1770408819597606</v>
+        <v>-0.1731606541188051</v>
       </c>
       <c r="J14" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K14" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03825134239141681</v>
+        <v>0.0367466668417421</v>
       </c>
       <c r="M14" t="n">
-        <v>5.031053235306342</v>
+        <v>5.033503059766509</v>
       </c>
       <c r="N14" t="n">
-        <v>40.99186620888091</v>
+        <v>41.02105787209261</v>
       </c>
       <c r="O14" t="n">
-        <v>6.402489063550278</v>
+        <v>6.404768369901648</v>
       </c>
       <c r="P14" t="n">
-        <v>387.1520287363299</v>
+        <v>387.1090216422818</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35261,28 +35346,28 @@
         <v>0.0313</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2186288604212454</v>
+        <v>-0.2143356033349233</v>
       </c>
       <c r="J15" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K15" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L15" t="n">
-        <v>0.056810962024749</v>
+        <v>0.05482231192668063</v>
       </c>
       <c r="M15" t="n">
-        <v>5.011213961761841</v>
+        <v>5.014892645719294</v>
       </c>
       <c r="N15" t="n">
-        <v>41.27786600995938</v>
+        <v>41.33620499888497</v>
       </c>
       <c r="O15" t="n">
-        <v>6.424785289016231</v>
+        <v>6.429323836834241</v>
       </c>
       <c r="P15" t="n">
-        <v>380.2055691856888</v>
+        <v>380.1579842193279</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35339,28 +35424,28 @@
         <v>0.0407</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1658203118387619</v>
+        <v>-0.1624934396829038</v>
       </c>
       <c r="J16" t="n">
+        <v>394</v>
+      </c>
+      <c r="K16" t="n">
         <v>393</v>
       </c>
-      <c r="K16" t="n">
-        <v>392</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.03288205326610838</v>
+        <v>0.0317269864224623</v>
       </c>
       <c r="M16" t="n">
-        <v>5.063889490246487</v>
+        <v>5.064417846253211</v>
       </c>
       <c r="N16" t="n">
-        <v>42.1129611294871</v>
+        <v>42.10347086516835</v>
       </c>
       <c r="O16" t="n">
-        <v>6.489449986669679</v>
+        <v>6.488718738331039</v>
       </c>
       <c r="P16" t="n">
-        <v>375.7938224995511</v>
+        <v>375.7569922909626</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35417,28 +35502,28 @@
         <v>0.0407</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1479177999171227</v>
+        <v>-0.1470133701596512</v>
       </c>
       <c r="J17" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K17" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02645947057599907</v>
+        <v>0.02629103511957676</v>
       </c>
       <c r="M17" t="n">
-        <v>5.024917337996251</v>
+        <v>5.016224534200524</v>
       </c>
       <c r="N17" t="n">
-        <v>41.87447905733613</v>
+        <v>41.77543706997862</v>
       </c>
       <c r="O17" t="n">
-        <v>6.471049301105357</v>
+        <v>6.463392071503834</v>
       </c>
       <c r="P17" t="n">
-        <v>369.8265627043732</v>
+        <v>369.8165383199212</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35495,28 +35580,28 @@
         <v>0.0417</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1301291043403092</v>
+        <v>-0.1287579887959353</v>
       </c>
       <c r="J18" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K18" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03180980143568468</v>
+        <v>0.03132294269995872</v>
       </c>
       <c r="M18" t="n">
-        <v>4.152520148468724</v>
+        <v>4.148388226054788</v>
       </c>
       <c r="N18" t="n">
-        <v>26.80922494063752</v>
+        <v>26.75781695707863</v>
       </c>
       <c r="O18" t="n">
-        <v>5.177762541932327</v>
+        <v>5.17279585495877</v>
       </c>
       <c r="P18" t="n">
-        <v>364.9115067421902</v>
+        <v>364.8963097750057</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35573,28 +35658,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1474228833246713</v>
+        <v>-0.1456054453191825</v>
       </c>
       <c r="J19" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K19" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0325408046745076</v>
+        <v>0.03192318913123626</v>
       </c>
       <c r="M19" t="n">
-        <v>4.51527392428852</v>
+        <v>4.511662468879086</v>
       </c>
       <c r="N19" t="n">
-        <v>33.61010153412455</v>
+        <v>33.55402564915605</v>
       </c>
       <c r="O19" t="n">
-        <v>5.797421973094985</v>
+        <v>5.792583676491524</v>
       </c>
       <c r="P19" t="n">
-        <v>366.7566997447532</v>
+        <v>366.7365558948475</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35651,28 +35736,28 @@
         <v>0.0363</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.144106503539452</v>
+        <v>-0.1424138475932939</v>
       </c>
       <c r="J20" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K20" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02754546325007035</v>
+        <v>0.02705641253201652</v>
       </c>
       <c r="M20" t="n">
-        <v>4.996611068505678</v>
+        <v>4.99205822813771</v>
       </c>
       <c r="N20" t="n">
-        <v>38.13484995704633</v>
+        <v>38.06341410864049</v>
       </c>
       <c r="O20" t="n">
-        <v>6.175342092309246</v>
+        <v>6.169555422284533</v>
       </c>
       <c r="P20" t="n">
-        <v>373.4017693110665</v>
+        <v>373.3830085020493</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -35729,28 +35814,28 @@
         <v>0.0421</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1313506365421733</v>
+        <v>-0.1312111612180282</v>
       </c>
       <c r="J21" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K21" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02781429285903281</v>
+        <v>0.02791587947778196</v>
       </c>
       <c r="M21" t="n">
-        <v>4.442174542964005</v>
+        <v>4.431629905802305</v>
       </c>
       <c r="N21" t="n">
-        <v>31.36759530282628</v>
+        <v>31.28815425948709</v>
       </c>
       <c r="O21" t="n">
-        <v>5.600678110981408</v>
+        <v>5.593581523450524</v>
       </c>
       <c r="P21" t="n">
-        <v>366.3660078368118</v>
+        <v>366.3644619408932</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -35807,28 +35892,28 @@
         <v>0.0345</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1136039229507787</v>
+        <v>-0.1134193061720851</v>
       </c>
       <c r="J22" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K22" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0218088599635623</v>
+        <v>0.02186477249880059</v>
       </c>
       <c r="M22" t="n">
-        <v>4.347856275441122</v>
+        <v>4.337663668407118</v>
       </c>
       <c r="N22" t="n">
-        <v>30.11016060776876</v>
+        <v>30.03404048372258</v>
       </c>
       <c r="O22" t="n">
-        <v>5.487272601918804</v>
+        <v>5.480332150857517</v>
       </c>
       <c r="P22" t="n">
-        <v>365.9840524896825</v>
+        <v>365.9820062616027</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -35866,7 +35951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W394"/>
+  <dimension ref="A1:W395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81963,6 +82048,123 @@
         </is>
       </c>
     </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:53:16+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>-37.6180821109188,177.9440523531629</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>-37.618017256257374,177.94496785388014</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>-37.617884412247705,177.94585631616584</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-37.61757923976054,177.94667624020826</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>-37.61726617974633,177.9474930258907</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>-37.616958750926614,177.9482716962607</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>-37.61670609309894,177.94896541952355</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>-37.61645024012775,177.9497338823461</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>-37.61614864041998,177.95056545446874</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>-37.615820459767626,177.95137300992138</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>-37.61544780958967,177.95214038319992</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>-37.61506597123974,177.95286751972347</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>-37.61462380988841,177.95351323649913</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>-37.614160463895495,177.95418538196702</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>-37.61367745716354,177.95484211047275</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>-37.613199856158765,177.95550898238585</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>-37.61265142579022,177.9560799031491</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>-37.61207135654637,177.95659806895705</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>-37.61147703888482,177.95705537793515</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>-37.61086783233273,177.95750579690096</t>
+        </is>
+      </c>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>-37.61021319891317,177.9578578840723</t>
+        </is>
+      </c>
+      <c r="W395" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0210/nzd0210.xlsx
+++ b/data/nzd0210/nzd0210.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W395"/>
+  <dimension ref="A1:W396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30093,6 +30093,81 @@
       <c r="W395" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:53:12+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>403.29</v>
+      </c>
+      <c r="C396" t="n">
+        <v>388.49</v>
+      </c>
+      <c r="D396" t="n">
+        <v>382.32</v>
+      </c>
+      <c r="E396" t="n">
+        <v>396.03</v>
+      </c>
+      <c r="F396" t="n">
+        <v>410.02</v>
+      </c>
+      <c r="G396" t="n">
+        <v>424.68</v>
+      </c>
+      <c r="H396" t="n">
+        <v>429.63</v>
+      </c>
+      <c r="I396" t="n">
+        <v>416.36</v>
+      </c>
+      <c r="J396" t="n">
+        <v>402.66</v>
+      </c>
+      <c r="K396" t="n">
+        <v>393.76</v>
+      </c>
+      <c r="L396" t="n">
+        <v>391.48</v>
+      </c>
+      <c r="M396" t="n">
+        <v>391.71</v>
+      </c>
+      <c r="N396" t="n">
+        <v>390.3</v>
+      </c>
+      <c r="O396" t="n">
+        <v>382.67</v>
+      </c>
+      <c r="P396" t="n">
+        <v>378.31</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>368.22</v>
+      </c>
+      <c r="R396" t="n">
+        <v>364.15</v>
+      </c>
+      <c r="S396" t="n">
+        <v>366.54</v>
+      </c>
+      <c r="T396" t="n">
+        <v>372.76</v>
+      </c>
+      <c r="U396" t="n">
+        <v>363.17</v>
+      </c>
+      <c r="V396" t="n">
+        <v>363.02</v>
+      </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -30107,7 +30182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B405"/>
+  <dimension ref="A1:B406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34160,6 +34235,16 @@
       </c>
       <c r="B405" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>-0.27</v>
       </c>
     </row>
   </sheetData>
@@ -34328,28 +34413,28 @@
         <v>0.0352</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2109966695444526</v>
+        <v>-0.2071156260705205</v>
       </c>
       <c r="J2" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K2" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1074161730528898</v>
+        <v>0.1038027228929974</v>
       </c>
       <c r="M2" t="n">
-        <v>3.690147123895121</v>
+        <v>3.700388986346324</v>
       </c>
       <c r="N2" t="n">
-        <v>19.3070708555563</v>
+        <v>19.39285620027705</v>
       </c>
       <c r="O2" t="n">
-        <v>4.39398120792025</v>
+        <v>4.40373207635036</v>
       </c>
       <c r="P2" t="n">
-        <v>401.6273311001974</v>
+        <v>401.5842781487316</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34406,28 +34491,28 @@
         <v>0.0504</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005286817963480347</v>
+        <v>0.004418875189743789</v>
       </c>
       <c r="J3" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K3" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L3" t="n">
-        <v>4.38650678002972e-07</v>
+        <v>3.069790756626833e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>4.63780123930361</v>
+        <v>4.644048455763063</v>
       </c>
       <c r="N3" t="n">
-        <v>33.25489428799948</v>
+        <v>33.30600440154701</v>
       </c>
       <c r="O3" t="n">
-        <v>5.766705670311211</v>
+        <v>5.771135451672142</v>
       </c>
       <c r="P3" t="n">
-        <v>381.1332122119806</v>
+        <v>381.0900577591939</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34484,28 +34569,28 @@
         <v>0.0418</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1480745550367445</v>
+        <v>0.152260338779782</v>
       </c>
       <c r="J4" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K4" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03281990565324522</v>
+        <v>0.03467640405776085</v>
       </c>
       <c r="M4" t="n">
-        <v>4.533041968257304</v>
+        <v>4.541340620026745</v>
       </c>
       <c r="N4" t="n">
-        <v>33.72226570364149</v>
+        <v>33.79353483076814</v>
       </c>
       <c r="O4" t="n">
-        <v>5.807087540552621</v>
+        <v>5.813220693451104</v>
       </c>
       <c r="P4" t="n">
-        <v>370.4516102702519</v>
+        <v>370.4051767928776</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -34566,28 +34651,28 @@
         <v>0.0581</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2116599174168961</v>
+        <v>0.2163348179485272</v>
       </c>
       <c r="J5" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K5" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09652037433144844</v>
+        <v>0.1001213300983419</v>
       </c>
       <c r="M5" t="n">
-        <v>3.572813574129582</v>
+        <v>3.585516113638149</v>
       </c>
       <c r="N5" t="n">
-        <v>21.88580182559037</v>
+        <v>22.02578335046406</v>
       </c>
       <c r="O5" t="n">
-        <v>4.678226354676563</v>
+        <v>4.693163469395037</v>
       </c>
       <c r="P5" t="n">
-        <v>381.5239728800776</v>
+        <v>381.4721135625904</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34644,28 +34729,28 @@
         <v>0.0635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1475064903206593</v>
+        <v>0.1509193171057162</v>
       </c>
       <c r="J6" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K6" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07755960029345854</v>
+        <v>0.08075817247075301</v>
       </c>
       <c r="M6" t="n">
-        <v>3.050172352412159</v>
+        <v>3.059030490173559</v>
       </c>
       <c r="N6" t="n">
-        <v>13.50550613847808</v>
+        <v>13.57544669484492</v>
       </c>
       <c r="O6" t="n">
-        <v>3.674983828328783</v>
+        <v>3.684487304204606</v>
       </c>
       <c r="P6" t="n">
-        <v>399.6233542573972</v>
+        <v>399.5854952983503</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34722,28 +34807,28 @@
         <v>0.0512</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05866650331816276</v>
+        <v>0.06218192948785027</v>
       </c>
       <c r="J7" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K7" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009954489223259255</v>
+        <v>0.01116572906316871</v>
       </c>
       <c r="M7" t="n">
-        <v>3.406659182542626</v>
+        <v>3.412402759287062</v>
       </c>
       <c r="N7" t="n">
-        <v>17.86497603031886</v>
+        <v>17.93023506304275</v>
       </c>
       <c r="O7" t="n">
-        <v>4.226698005573483</v>
+        <v>4.234410828325796</v>
       </c>
       <c r="P7" t="n">
-        <v>416.4762565168109</v>
+        <v>416.4372594086151</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34800,28 +34885,28 @@
         <v>0.0457</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01194414065387266</v>
+        <v>-0.00640232417304888</v>
       </c>
       <c r="J8" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K8" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00033587652258249</v>
+        <v>9.590119890579007e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.710635550104565</v>
+        <v>3.725658073081211</v>
       </c>
       <c r="N8" t="n">
-        <v>22.16001897803164</v>
+        <v>22.37849127278242</v>
       </c>
       <c r="O8" t="n">
-        <v>4.707442934123752</v>
+        <v>4.730591006711785</v>
       </c>
       <c r="P8" t="n">
-        <v>419.4882388087111</v>
+        <v>419.4267626728255</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34878,28 +34963,28 @@
         <v>0.055</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.09517608502737383</v>
+        <v>-0.08947711310674829</v>
       </c>
       <c r="J9" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K9" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02244590394223756</v>
+        <v>0.0197309844489183</v>
       </c>
       <c r="M9" t="n">
-        <v>3.613455418847179</v>
+        <v>3.633280183435685</v>
       </c>
       <c r="N9" t="n">
-        <v>20.58947272453306</v>
+        <v>20.82771467004624</v>
       </c>
       <c r="O9" t="n">
-        <v>4.537562421006796</v>
+        <v>4.56373911064669</v>
       </c>
       <c r="P9" t="n">
-        <v>408.1548622880152</v>
+        <v>408.091642805123</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34956,28 +35041,28 @@
         <v>0.058</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0986241854014675</v>
+        <v>-0.09408486308865771</v>
       </c>
       <c r="J10" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K10" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02424680365330678</v>
+        <v>0.02204616519904767</v>
       </c>
       <c r="M10" t="n">
-        <v>3.651165463873729</v>
+        <v>3.661467236198562</v>
       </c>
       <c r="N10" t="n">
-        <v>20.42858082609955</v>
+        <v>20.5610828046476</v>
       </c>
       <c r="O10" t="n">
-        <v>4.519798759469226</v>
+        <v>4.534433019093743</v>
       </c>
       <c r="P10" t="n">
-        <v>396.7436070614148</v>
+        <v>396.6932517318406</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35034,28 +35119,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.179922607285329</v>
+        <v>-0.1760303204339013</v>
       </c>
       <c r="J11" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K11" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07620717519039522</v>
+        <v>0.07313222250230433</v>
       </c>
       <c r="M11" t="n">
-        <v>3.639109075074707</v>
+        <v>3.647305884012755</v>
       </c>
       <c r="N11" t="n">
-        <v>20.48028730603269</v>
+        <v>20.56388385557314</v>
       </c>
       <c r="O11" t="n">
-        <v>4.52551514261445</v>
+        <v>4.534741873091912</v>
       </c>
       <c r="P11" t="n">
-        <v>391.2395103788973</v>
+        <v>391.1963327030913</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35112,28 +35197,28 @@
         <v>0.0613</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1480909874312359</v>
+        <v>-0.1442601048165394</v>
       </c>
       <c r="J12" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K12" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05166267193349994</v>
+        <v>0.04913530372740316</v>
       </c>
       <c r="M12" t="n">
-        <v>3.726661972316859</v>
+        <v>3.736820339126077</v>
       </c>
       <c r="N12" t="n">
-        <v>21.01014702799853</v>
+        <v>21.08816233081306</v>
       </c>
       <c r="O12" t="n">
-        <v>4.583682692769923</v>
+        <v>4.592184919056837</v>
       </c>
       <c r="P12" t="n">
-        <v>388.2263139502697</v>
+        <v>388.1838174401456</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35190,28 +35275,28 @@
         <v>0.0355</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2103143859894805</v>
+        <v>-0.2061926219987546</v>
       </c>
       <c r="J13" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K13" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05820576415837908</v>
+        <v>0.05616718142542598</v>
       </c>
       <c r="M13" t="n">
-        <v>4.830054426128003</v>
+        <v>4.840033265066308</v>
       </c>
       <c r="N13" t="n">
-        <v>37.35199869004775</v>
+        <v>37.40932372019018</v>
       </c>
       <c r="O13" t="n">
-        <v>6.111628153777661</v>
+        <v>6.116316188702982</v>
       </c>
       <c r="P13" t="n">
-        <v>389.5747617096005</v>
+        <v>389.5290384121836</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35268,28 +35353,28 @@
         <v>0.0322</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1731606541188051</v>
+        <v>-0.1690103433243534</v>
       </c>
       <c r="J14" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K14" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0367466668417421</v>
+        <v>0.03513787935144919</v>
       </c>
       <c r="M14" t="n">
-        <v>5.033503059766509</v>
+        <v>5.037079477395683</v>
       </c>
       <c r="N14" t="n">
-        <v>41.02105787209261</v>
+        <v>41.07120533059651</v>
       </c>
       <c r="O14" t="n">
-        <v>6.404768369901648</v>
+        <v>6.408682027577629</v>
       </c>
       <c r="P14" t="n">
-        <v>387.1090216422818</v>
+        <v>387.0629816712271</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35346,28 +35431,28 @@
         <v>0.0313</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2143356033349233</v>
+        <v>-0.2099577625100445</v>
       </c>
       <c r="J15" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K15" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05482231192668063</v>
+        <v>0.05280714263026609</v>
       </c>
       <c r="M15" t="n">
-        <v>5.014892645719294</v>
+        <v>5.018956760047508</v>
       </c>
       <c r="N15" t="n">
-        <v>41.33620499888497</v>
+        <v>41.40290256607631</v>
       </c>
       <c r="O15" t="n">
-        <v>6.429323836834241</v>
+        <v>6.434508727640075</v>
       </c>
       <c r="P15" t="n">
-        <v>380.1579842193279</v>
+        <v>380.1094202262098</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35424,28 +35509,28 @@
         <v>0.0407</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1624934396829038</v>
+        <v>-0.1588217274182059</v>
       </c>
       <c r="J16" t="n">
+        <v>395</v>
+      </c>
+      <c r="K16" t="n">
         <v>394</v>
       </c>
-      <c r="K16" t="n">
-        <v>393</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.0317269864224623</v>
+        <v>0.03044095371932465</v>
       </c>
       <c r="M16" t="n">
-        <v>5.064417846253211</v>
+        <v>5.066545196430227</v>
       </c>
       <c r="N16" t="n">
-        <v>42.10347086516835</v>
+        <v>42.1168080750963</v>
       </c>
       <c r="O16" t="n">
-        <v>6.488718738331039</v>
+        <v>6.489746379874664</v>
       </c>
       <c r="P16" t="n">
-        <v>375.7569922909626</v>
+        <v>375.7163097385407</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35502,28 +35587,28 @@
         <v>0.0407</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1470133701596512</v>
+        <v>-0.1457676340949951</v>
       </c>
       <c r="J17" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K17" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02629103511957676</v>
+        <v>0.02599791748558244</v>
       </c>
       <c r="M17" t="n">
-        <v>5.016224534200524</v>
+        <v>5.009092267080365</v>
       </c>
       <c r="N17" t="n">
-        <v>41.77543706997862</v>
+        <v>41.68355062624047</v>
       </c>
       <c r="O17" t="n">
-        <v>6.463392071503834</v>
+        <v>6.456279937103136</v>
       </c>
       <c r="P17" t="n">
-        <v>369.8165383199212</v>
+        <v>369.8027191976436</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35580,28 +35665,28 @@
         <v>0.0417</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1287579887959353</v>
+        <v>-0.1273205042297043</v>
       </c>
       <c r="J18" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K18" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03132294269995872</v>
+        <v>0.03080207962272175</v>
       </c>
       <c r="M18" t="n">
-        <v>4.148388226054788</v>
+        <v>4.144572301381444</v>
       </c>
       <c r="N18" t="n">
-        <v>26.75781695707863</v>
+        <v>26.70854964634988</v>
       </c>
       <c r="O18" t="n">
-        <v>5.17279585495877</v>
+        <v>5.168031505936266</v>
       </c>
       <c r="P18" t="n">
-        <v>364.8963097750057</v>
+        <v>364.8803635601079</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35658,28 +35743,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1456054453191825</v>
+        <v>-0.1436420201336929</v>
       </c>
       <c r="J19" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K19" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03192318913123626</v>
+        <v>0.03123990257446474</v>
       </c>
       <c r="M19" t="n">
-        <v>4.511662468879086</v>
+        <v>4.508680892453287</v>
       </c>
       <c r="N19" t="n">
-        <v>33.55402564915605</v>
+        <v>33.50354414113044</v>
       </c>
       <c r="O19" t="n">
-        <v>5.792583676491524</v>
+        <v>5.788224610459622</v>
       </c>
       <c r="P19" t="n">
-        <v>366.7365558948475</v>
+        <v>366.7147753479956</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35736,28 +35821,28 @@
         <v>0.0363</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1424138475932939</v>
+        <v>-0.1407202701643922</v>
       </c>
       <c r="J20" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K20" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02705641253201652</v>
+        <v>0.02656687812879543</v>
       </c>
       <c r="M20" t="n">
-        <v>4.99205822813771</v>
+        <v>4.987516910332936</v>
       </c>
       <c r="N20" t="n">
-        <v>38.06341410864049</v>
+        <v>37.9926937865711</v>
       </c>
       <c r="O20" t="n">
-        <v>6.169555422284533</v>
+        <v>6.163821362318274</v>
       </c>
       <c r="P20" t="n">
-        <v>373.3830085020493</v>
+        <v>373.3642214136439</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -35814,28 +35899,28 @@
         <v>0.0421</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1312111612180282</v>
+        <v>-0.1310402717296711</v>
       </c>
       <c r="J21" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K21" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02791587947778196</v>
+        <v>0.02800352655783145</v>
       </c>
       <c r="M21" t="n">
-        <v>4.431629905802305</v>
+        <v>4.421301017810351</v>
       </c>
       <c r="N21" t="n">
-        <v>31.28815425948709</v>
+        <v>31.20920482935206</v>
       </c>
       <c r="O21" t="n">
-        <v>5.593581523450524</v>
+        <v>5.58651992114519</v>
       </c>
       <c r="P21" t="n">
-        <v>366.3644619408932</v>
+        <v>366.3625662401885</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -35892,28 +35977,28 @@
         <v>0.0345</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1134193061720851</v>
+        <v>-0.1133778229231211</v>
       </c>
       <c r="J22" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K22" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02186477249880059</v>
+        <v>0.02197427547938158</v>
       </c>
       <c r="M22" t="n">
-        <v>4.337663668407118</v>
+        <v>4.326870708361251</v>
       </c>
       <c r="N22" t="n">
-        <v>30.03404048372258</v>
+        <v>29.95802032328405</v>
       </c>
       <c r="O22" t="n">
-        <v>5.480332150857517</v>
+        <v>5.473392030841939</v>
       </c>
       <c r="P22" t="n">
-        <v>365.9820062616027</v>
+        <v>365.9815460821906</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -35951,7 +36036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W395"/>
+  <dimension ref="A1:W396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82165,6 +82250,123 @@
         </is>
       </c>
     </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:53:12+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>-37.61808253959818,177.9440525236493</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>-37.61801862802733,177.94496839944705</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>-37.617880725626215,177.94585484993004</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>-37.61757238094635,177.9466735122959</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>-37.617261635792815,177.94749121862796</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>-37.61695614004202,177.94827046829502</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>-37.61670281048854,177.9489630715026</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>-37.616443522545474,177.94972781215074</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>-37.61614885947048,177.95056565241057</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>-37.615819145470866,177.95137182226733</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>-37.61544109210206,177.9521343129604</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>-37.61505899301908,177.95286021215333</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>-37.61461995001521,177.95350817920695</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>-37.61415879404236,177.95418301305918</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>-37.61367317783571,177.95483570467326</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>-37.61319631166138,177.9555029984549</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>-37.612650603673295,177.95607841887485</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>-37.612069682713475,177.95659498878248</t>
+        </is>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>-37.61147683128227,177.95705487660766</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>-37.61086763733802,177.9575051645299</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>-37.61021404388591,177.95786062432387</t>
+        </is>
+      </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0210/nzd0210.xlsx
+++ b/data/nzd0210/nzd0210.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W396"/>
+  <dimension ref="A1:W398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30168,6 +30168,156 @@
       <c r="W396" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:27+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>404.26</v>
+      </c>
+      <c r="C397" t="n">
+        <v>389.7</v>
+      </c>
+      <c r="D397" t="n">
+        <v>384.21</v>
+      </c>
+      <c r="E397" t="n">
+        <v>397.74</v>
+      </c>
+      <c r="F397" t="n">
+        <v>411.41</v>
+      </c>
+      <c r="G397" t="n">
+        <v>425.5</v>
+      </c>
+      <c r="H397" t="n">
+        <v>430.74</v>
+      </c>
+      <c r="I397" t="n">
+        <v>416.66</v>
+      </c>
+      <c r="J397" t="n">
+        <v>403.33</v>
+      </c>
+      <c r="K397" t="n">
+        <v>394.81</v>
+      </c>
+      <c r="L397" t="n">
+        <v>392.74</v>
+      </c>
+      <c r="M397" t="n">
+        <v>393.39</v>
+      </c>
+      <c r="N397" t="n">
+        <v>390.57</v>
+      </c>
+      <c r="O397" t="n">
+        <v>382.96</v>
+      </c>
+      <c r="P397" t="n">
+        <v>379.29</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>369.13</v>
+      </c>
+      <c r="R397" t="n">
+        <v>363.35</v>
+      </c>
+      <c r="S397" t="n">
+        <v>366.3</v>
+      </c>
+      <c r="T397" t="n">
+        <v>371.77</v>
+      </c>
+      <c r="U397" t="n">
+        <v>361.98</v>
+      </c>
+      <c r="V397" t="n">
+        <v>361.4</v>
+      </c>
+      <c r="W397" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>406.48</v>
+      </c>
+      <c r="C398" t="n">
+        <v>391.56</v>
+      </c>
+      <c r="D398" t="n">
+        <v>385.05</v>
+      </c>
+      <c r="E398" t="n">
+        <v>398.53</v>
+      </c>
+      <c r="F398" t="n">
+        <v>411.95</v>
+      </c>
+      <c r="G398" t="n">
+        <v>425.27</v>
+      </c>
+      <c r="H398" t="n">
+        <v>430.66</v>
+      </c>
+      <c r="I398" t="n">
+        <v>417.61</v>
+      </c>
+      <c r="J398" t="n">
+        <v>405.04</v>
+      </c>
+      <c r="K398" t="n">
+        <v>395.18</v>
+      </c>
+      <c r="L398" t="n">
+        <v>392.86</v>
+      </c>
+      <c r="M398" t="n">
+        <v>392.99</v>
+      </c>
+      <c r="N398" t="n">
+        <v>391.31</v>
+      </c>
+      <c r="O398" t="n">
+        <v>383.6</v>
+      </c>
+      <c r="P398" t="n">
+        <v>380.26</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>369.42</v>
+      </c>
+      <c r="R398" t="n">
+        <v>363.17</v>
+      </c>
+      <c r="S398" t="n">
+        <v>366.97</v>
+      </c>
+      <c r="T398" t="n">
+        <v>370.9</v>
+      </c>
+      <c r="U398" t="n">
+        <v>360.72</v>
+      </c>
+      <c r="V398" t="n">
+        <v>361.38</v>
+      </c>
+      <c r="W398" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -30182,7 +30332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B406"/>
+  <dimension ref="A1:B408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34245,6 +34395,26 @@
       </c>
       <c r="B406" t="n">
         <v>-0.27</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -34413,28 +34583,28 @@
         <v>0.0352</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2071156260705205</v>
+        <v>-0.1972432863245906</v>
       </c>
       <c r="J2" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K2" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1038027228929974</v>
+        <v>0.09413201740746846</v>
       </c>
       <c r="M2" t="n">
-        <v>3.700388986346324</v>
+        <v>3.731595000896455</v>
       </c>
       <c r="N2" t="n">
-        <v>19.39285620027705</v>
+        <v>19.73604240645898</v>
       </c>
       <c r="O2" t="n">
-        <v>4.40373207635036</v>
+        <v>4.442526579150538</v>
       </c>
       <c r="P2" t="n">
-        <v>401.5842781487316</v>
+        <v>401.4742334132778</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34491,28 +34661,28 @@
         <v>0.0504</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004418875189743789</v>
+        <v>0.0143488908370476</v>
       </c>
       <c r="J3" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K3" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L3" t="n">
-        <v>3.069790756626833e-05</v>
+        <v>0.0003230829707212557</v>
       </c>
       <c r="M3" t="n">
-        <v>4.644048455763063</v>
+        <v>4.66623170252516</v>
       </c>
       <c r="N3" t="n">
-        <v>33.30600440154701</v>
+        <v>33.58229143859237</v>
       </c>
       <c r="O3" t="n">
-        <v>5.771135451672142</v>
+        <v>5.795022988616385</v>
       </c>
       <c r="P3" t="n">
-        <v>381.0900577591939</v>
+        <v>380.9793730752565</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34569,28 +34739,28 @@
         <v>0.0418</v>
       </c>
       <c r="I4" t="n">
-        <v>0.152260338779782</v>
+        <v>0.1629292761155919</v>
       </c>
       <c r="J4" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K4" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03467640405776085</v>
+        <v>0.03938355705902075</v>
       </c>
       <c r="M4" t="n">
-        <v>4.541340620026745</v>
+        <v>4.568187004948549</v>
       </c>
       <c r="N4" t="n">
-        <v>33.79353483076814</v>
+        <v>34.13197353670349</v>
       </c>
       <c r="O4" t="n">
-        <v>5.813220693451104</v>
+        <v>5.842257571924016</v>
       </c>
       <c r="P4" t="n">
-        <v>370.4051767928776</v>
+        <v>370.286264427898</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -34651,28 +34821,28 @@
         <v>0.0581</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2163348179485272</v>
+        <v>0.2277464596273688</v>
       </c>
       <c r="J5" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K5" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1001213300983419</v>
+        <v>0.1083678786922856</v>
       </c>
       <c r="M5" t="n">
-        <v>3.585516113638149</v>
+        <v>3.620316770049162</v>
       </c>
       <c r="N5" t="n">
-        <v>22.02578335046406</v>
+        <v>22.49657837511122</v>
       </c>
       <c r="O5" t="n">
-        <v>4.693163469395037</v>
+        <v>4.743055805607944</v>
       </c>
       <c r="P5" t="n">
-        <v>381.4721135625904</v>
+        <v>381.3449240971133</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34729,28 +34899,28 @@
         <v>0.0635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1509193171057162</v>
+        <v>0.1593757559139646</v>
       </c>
       <c r="J6" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K6" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08075817247075301</v>
+        <v>0.08829129248171697</v>
       </c>
       <c r="M6" t="n">
-        <v>3.059030490173559</v>
+        <v>3.084107677475051</v>
       </c>
       <c r="N6" t="n">
-        <v>13.57544669484492</v>
+        <v>13.82645389846009</v>
       </c>
       <c r="O6" t="n">
-        <v>3.684487304204606</v>
+        <v>3.718393994517</v>
       </c>
       <c r="P6" t="n">
-        <v>399.5854952983503</v>
+        <v>399.4912436930369</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34807,28 +34977,28 @@
         <v>0.0512</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06218192948785027</v>
+        <v>0.06984743927399684</v>
       </c>
       <c r="J7" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K7" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01116572906316871</v>
+        <v>0.0140078315922626</v>
       </c>
       <c r="M7" t="n">
-        <v>3.412402759287062</v>
+        <v>3.426580077995835</v>
       </c>
       <c r="N7" t="n">
-        <v>17.93023506304275</v>
+        <v>18.10220994926578</v>
       </c>
       <c r="O7" t="n">
-        <v>4.234410828325796</v>
+        <v>4.254669193869927</v>
       </c>
       <c r="P7" t="n">
-        <v>416.4372594086151</v>
+        <v>416.3518284651294</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34885,28 +35055,28 @@
         <v>0.0457</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.00640232417304888</v>
+        <v>0.005656476761772696</v>
       </c>
       <c r="J8" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K8" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L8" t="n">
-        <v>9.590119890579007e-05</v>
+        <v>7.359943851437123e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.725658073081211</v>
+        <v>3.759707410144756</v>
       </c>
       <c r="N8" t="n">
-        <v>22.37849127278242</v>
+        <v>22.91467040011636</v>
       </c>
       <c r="O8" t="n">
-        <v>4.730591006711785</v>
+        <v>4.786927030999779</v>
       </c>
       <c r="P8" t="n">
-        <v>419.4267626728255</v>
+        <v>419.2923669924684</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34963,28 +35133,28 @@
         <v>0.055</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08947711310674829</v>
+        <v>-0.07740507626448176</v>
       </c>
       <c r="J9" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K9" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0197309844489183</v>
+        <v>0.01456158554800846</v>
       </c>
       <c r="M9" t="n">
-        <v>3.633280183435685</v>
+        <v>3.675801399596809</v>
       </c>
       <c r="N9" t="n">
-        <v>20.82771467004624</v>
+        <v>21.37409690997317</v>
       </c>
       <c r="O9" t="n">
-        <v>4.56373911064669</v>
+        <v>4.623212834163399</v>
       </c>
       <c r="P9" t="n">
-        <v>408.091642805123</v>
+        <v>407.9570918660349</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35041,28 +35211,28 @@
         <v>0.058</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09408486308865771</v>
+        <v>-0.08351874635240897</v>
       </c>
       <c r="J10" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K10" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02204616519904767</v>
+        <v>0.01724127910242179</v>
       </c>
       <c r="M10" t="n">
-        <v>3.661467236198562</v>
+        <v>3.687814829145751</v>
       </c>
       <c r="N10" t="n">
-        <v>20.5610828046476</v>
+        <v>20.95913833461382</v>
       </c>
       <c r="O10" t="n">
-        <v>4.534433019093743</v>
+        <v>4.578115150868731</v>
       </c>
       <c r="P10" t="n">
-        <v>396.6932517318406</v>
+        <v>396.5754786898222</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35119,28 +35289,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1760303204339013</v>
+        <v>-0.1670285331059851</v>
       </c>
       <c r="J11" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K11" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07313222250230433</v>
+        <v>0.06597012361368915</v>
       </c>
       <c r="M11" t="n">
-        <v>3.647305884012755</v>
+        <v>3.668917942266865</v>
       </c>
       <c r="N11" t="n">
-        <v>20.56388385557314</v>
+        <v>20.82202054495651</v>
       </c>
       <c r="O11" t="n">
-        <v>4.534741873091912</v>
+        <v>4.563115223721237</v>
       </c>
       <c r="P11" t="n">
-        <v>391.1963327030913</v>
+        <v>391.0960042219587</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35197,28 +35367,28 @@
         <v>0.0613</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1442601048165394</v>
+        <v>-0.1352980863643954</v>
       </c>
       <c r="J12" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K12" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04913530372740316</v>
+        <v>0.04326166486595595</v>
       </c>
       <c r="M12" t="n">
-        <v>3.736820339126077</v>
+        <v>3.763948512583573</v>
       </c>
       <c r="N12" t="n">
-        <v>21.08816233081306</v>
+        <v>21.34033937559928</v>
       </c>
       <c r="O12" t="n">
-        <v>4.592184919056837</v>
+        <v>4.619560517581654</v>
       </c>
       <c r="P12" t="n">
-        <v>388.1838174401456</v>
+        <v>388.0839340579173</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35275,28 +35445,28 @@
         <v>0.0355</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2061926219987546</v>
+        <v>-0.1964790989983601</v>
       </c>
       <c r="J13" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K13" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05616718142542598</v>
+        <v>0.05128857752062876</v>
       </c>
       <c r="M13" t="n">
-        <v>4.840033265066308</v>
+        <v>4.867864935947693</v>
       </c>
       <c r="N13" t="n">
-        <v>37.40932372019018</v>
+        <v>37.64213583840852</v>
       </c>
       <c r="O13" t="n">
-        <v>6.116316188702982</v>
+        <v>6.135318723457528</v>
       </c>
       <c r="P13" t="n">
-        <v>389.5290384121836</v>
+        <v>389.4207833147117</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35353,28 +35523,28 @@
         <v>0.0322</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1690103433243534</v>
+        <v>-0.1601200184393468</v>
       </c>
       <c r="J14" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K14" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03513787935144919</v>
+        <v>0.03174860484622455</v>
       </c>
       <c r="M14" t="n">
-        <v>5.037079477395683</v>
+        <v>5.04654425810688</v>
       </c>
       <c r="N14" t="n">
-        <v>41.07120533059651</v>
+        <v>41.21761091162927</v>
       </c>
       <c r="O14" t="n">
-        <v>6.408682027577629</v>
+        <v>6.420094307066623</v>
       </c>
       <c r="P14" t="n">
-        <v>387.0629816712271</v>
+        <v>386.9638926867727</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35431,28 +35601,28 @@
         <v>0.0313</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2099577625100445</v>
+        <v>-0.2006528283924544</v>
       </c>
       <c r="J15" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K15" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05280714263026609</v>
+        <v>0.04856266649117702</v>
       </c>
       <c r="M15" t="n">
-        <v>5.018956760047508</v>
+        <v>5.028653386706803</v>
       </c>
       <c r="N15" t="n">
-        <v>41.40290256607631</v>
+        <v>41.58113138265487</v>
       </c>
       <c r="O15" t="n">
-        <v>6.434508727640075</v>
+        <v>6.448343305272671</v>
       </c>
       <c r="P15" t="n">
-        <v>380.1094202262098</v>
+        <v>380.0057111501484</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35509,28 +35679,28 @@
         <v>0.0407</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1588217274182059</v>
+        <v>-0.1500134101701542</v>
       </c>
       <c r="J16" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K16" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03044095371932465</v>
+        <v>0.02734191226128713</v>
       </c>
       <c r="M16" t="n">
-        <v>5.066545196430227</v>
+        <v>5.07691095063214</v>
       </c>
       <c r="N16" t="n">
-        <v>42.1168080750963</v>
+        <v>42.2505004493441</v>
       </c>
       <c r="O16" t="n">
-        <v>6.489746379874664</v>
+        <v>6.500038495989397</v>
       </c>
       <c r="P16" t="n">
-        <v>375.7163097385407</v>
+        <v>375.6182493601374</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35587,28 +35757,28 @@
         <v>0.0407</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1457676340949951</v>
+        <v>-0.1421864168372243</v>
       </c>
       <c r="J17" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K17" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02599791748558244</v>
+        <v>0.02501895966759748</v>
       </c>
       <c r="M17" t="n">
-        <v>5.009092267080365</v>
+        <v>4.999590293481022</v>
       </c>
       <c r="N17" t="n">
-        <v>41.68355062624047</v>
+        <v>41.5308872872011</v>
       </c>
       <c r="O17" t="n">
-        <v>6.456279937103136</v>
+        <v>6.444446235884127</v>
       </c>
       <c r="P17" t="n">
-        <v>369.8027191976436</v>
+        <v>369.7628040007803</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35665,28 +35835,28 @@
         <v>0.0417</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1273205042297043</v>
+        <v>-0.1254122089352412</v>
       </c>
       <c r="J18" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K18" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03080207962272175</v>
+        <v>0.03023777808306127</v>
       </c>
       <c r="M18" t="n">
-        <v>4.144572301381444</v>
+        <v>4.132453772645765</v>
       </c>
       <c r="N18" t="n">
-        <v>26.70854964634988</v>
+        <v>26.59029082704954</v>
       </c>
       <c r="O18" t="n">
-        <v>5.168031505936266</v>
+        <v>5.156577433438728</v>
       </c>
       <c r="P18" t="n">
-        <v>364.8803635601079</v>
+        <v>364.8590967706139</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35743,28 +35913,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1436420201336929</v>
+        <v>-0.1396463274613301</v>
       </c>
       <c r="J19" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K19" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03123990257446474</v>
+        <v>0.02985334749457957</v>
       </c>
       <c r="M19" t="n">
-        <v>4.508680892453287</v>
+        <v>4.503087059011158</v>
       </c>
       <c r="N19" t="n">
-        <v>33.50354414113044</v>
+        <v>33.40653693845304</v>
       </c>
       <c r="O19" t="n">
-        <v>5.788224610459622</v>
+        <v>5.779838833259371</v>
       </c>
       <c r="P19" t="n">
-        <v>366.7147753479956</v>
+        <v>366.6702379996293</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35821,28 +35991,28 @@
         <v>0.0363</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1407202701643922</v>
+        <v>-0.1388615624098291</v>
       </c>
       <c r="J20" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K20" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02656687812879543</v>
+        <v>0.02617450694830203</v>
       </c>
       <c r="M20" t="n">
-        <v>4.987516910332936</v>
+        <v>4.971143461536627</v>
       </c>
       <c r="N20" t="n">
-        <v>37.9926937865711</v>
+        <v>37.81767203045344</v>
       </c>
       <c r="O20" t="n">
-        <v>6.163821362318274</v>
+        <v>6.14960746962385</v>
       </c>
       <c r="P20" t="n">
-        <v>373.3642214136439</v>
+        <v>373.3435124516532</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -35899,28 +36069,28 @@
         <v>0.0421</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1310402717296711</v>
+        <v>-0.1326005613128498</v>
       </c>
       <c r="J21" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K21" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02800352655783145</v>
+        <v>0.02897222236991148</v>
       </c>
       <c r="M21" t="n">
-        <v>4.421301017810351</v>
+        <v>4.405682004821506</v>
       </c>
       <c r="N21" t="n">
-        <v>31.20920482935206</v>
+        <v>31.06480524485065</v>
       </c>
       <c r="O21" t="n">
-        <v>5.58651992114519</v>
+        <v>5.573581007292407</v>
       </c>
       <c r="P21" t="n">
-        <v>366.3625662401885</v>
+        <v>366.3799652209648</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -35977,28 +36147,28 @@
         <v>0.0345</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1133778229231211</v>
+        <v>-0.1149916474072172</v>
       </c>
       <c r="J22" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K22" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02197427547938158</v>
+        <v>0.02284211939965808</v>
       </c>
       <c r="M22" t="n">
-        <v>4.326870708361251</v>
+        <v>4.313033079918983</v>
       </c>
       <c r="N22" t="n">
-        <v>29.95802032328405</v>
+        <v>29.81872018703644</v>
       </c>
       <c r="O22" t="n">
-        <v>5.473392030841939</v>
+        <v>5.46065199285181</v>
       </c>
       <c r="P22" t="n">
-        <v>365.9815460821906</v>
+        <v>365.9995323677607</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36036,7 +36206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W396"/>
+  <dimension ref="A1:W398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82367,6 +82537,240 @@
         </is>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:27+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>-37.61807422321832,177.94404921621333</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>-37.618008254016964,177.94496427359798</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>-37.61786452163839,177.94584840531428</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>-37.61755772023069,177.94666768138515</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>-37.61724971863147,177.94748647882682</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>-37.616949233831036,177.9482672201283</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>-37.616694135017894,177.94895686601973</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>-37.616441332029424,177.94972583273946</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>-37.61614396734259,177.95056123170994</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>-37.6158114787395,177.95136489428634</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>-37.615431892064024,177.9521259993733</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>-37.61504738568053,177.95284805699023</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>-37.61461826910259,177.95350597683796</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>-37.614157064551556,177.9541805595476</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>-37.61366751061714,177.95482722131823</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>-37.61319142455079,177.95549474788436</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>-37.612654714257694,177.95608584024637</t>
+        </is>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>-37.61207090004649,177.95659722890943</t>
+        </is>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>-37.61148094181224,177.95706480289252</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>-37.61087150473229,177.95751770655656</t>
+        </is>
+      </c>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>-37.6102193087146,177.95787769820024</t>
+        </is>
+      </c>
+      <c r="W397" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>-37.61805518985355,177.94404164662066</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>-37.61799230719066,177.94495793138617</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>-37.61785731986585,177.94584554104165</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>-37.617550947151365,177.94666498757343</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>-37.61724508894282,177.94748463746566</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>-37.616951170939004,177.94826813119937</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>-37.61669476027705,177.94895731326167</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>-37.61643439539501,177.94971956460452</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>-37.616131481463,177.95054994902904</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>-37.615808777129274,177.95136245299813</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>-37.61543101586987,177.95212520760322</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>-37.6150501493327,177.95285095107633</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>-37.614613662156714,177.95349994071597</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>-37.61415324774402,177.95417514490182</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>-37.613661901226635,177.95481882452935</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>-37.61318986711981,177.95549211858184</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>-37.61265563913912,177.95608751005506</t>
+        </is>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>-37.612067501658366,177.95659097522184</t>
+        </is>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>-37.61148455409539,177.9570735259922</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>-37.61087559961877,177.95753098635078</t>
+        </is>
+      </c>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>-37.61021937371247,177.95787790898885</t>
+        </is>
+      </c>
+      <c r="W398" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
